--- a/etf_holdings/2026-08-28_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-28_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,17 +464,77 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>00981A(-620,000)、00991A(-200,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>全部加碼</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>00407A(1,294)、00993A(1,872)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>全部減碼</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>00991A(-80,000)、00407A(-20,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-28_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-28_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -474,19 +474,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00981A(-620,000)、00991A(-200,000)</t>
+          <t>00981A(-620,000)、00991A(-200,000)、00403A(-900,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,47 +494,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00407A(1,294)、00993A(1,872)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>旺矽科技</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>全部減碼</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00991A(-80,000)、00407A(-20,000)</t>
+          <t>00981A(-28,000)、00403A(-30,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-28_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-28_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -474,19 +474,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00981A(-620,000)、00991A(-200,000)、00403A(-900,000)</t>
+          <t>00981A(-620,000)、00991A(-200,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,17 +494,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>00407A(1,294)、00993A(1,872)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>全部減碼</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>00981A(-28,000)、00403A(-30,000)</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>00991A(-80,000)、00407A(-20,000)</t>
         </is>
       </c>
     </row>

--- a/etf_holdings/2026-08-28_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-08-28_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -474,19 +474,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>00981A(-620,000)、00991A(-200,000)</t>
+          <t>00981A(-620,000)、00991A(-200,000)、00403A(-900,000)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,29 +494,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>全部減碼</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00407A(1,294)、00993A(1,872)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00981A(-28,000)、00403A(-30,000)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>旺矽科技</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -524,15 +524,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>00407A(1,294)、00993A(1,872)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>旺矽科技</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>全部減碼</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>00991A(-80,000)、00407A(-20,000)</t>
         </is>
